--- a/NikolicNenad/opravljenoDelo/NikolicNenad.xlsx
+++ b/NikolicNenad/opravljenoDelo/NikolicNenad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikol\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikol\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5416CF-5920-4A57-A7A7-DCA46E688590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EA46DE-40A6-423A-9F32-3C31DE2F817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,12 +449,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -649,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -683,6 +677,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -702,26 +702,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1503,37 +1490,37 @@
       <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="23" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1573,33 +1560,33 @@
       <c r="N3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B4" s="23">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="P4" s="18" t="s">
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="P4" s="20" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1610,32 +1597,32 @@
       <c r="C5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="23" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="13"/>
-      <c r="P5" s="19" t="s">
+      <c r="N5" s="15"/>
+      <c r="P5" s="21" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1664,34 +1651,34 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="13"/>
+      <c r="N6" s="15"/>
     </row>
     <row r="7" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="23">
+      <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="25"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="15"/>
     </row>
     <row r="8" spans="2:16" ht="285" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
@@ -1712,38 +1699,38 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="13"/>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="23">
+      <c r="B9" s="9">
         <v>3</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="25"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="15"/>
     </row>
     <row r="10" spans="2:16" ht="120" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
@@ -1770,7 +1757,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="13"/>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
@@ -1779,10 +1766,10 @@
       <c r="C11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="23" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="4"/>
@@ -1793,7 +1780,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="13"/>
+      <c r="N11" s="15"/>
     </row>
     <row r="12" spans="2:16" ht="195" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
@@ -1812,34 +1799,34 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="13"/>
+      <c r="N12" s="15"/>
     </row>
     <row r="13" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="23">
+      <c r="B13" s="9">
         <v>4</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="25"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="15"/>
     </row>
     <row r="14" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
@@ -1858,7 +1845,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="13"/>
+      <c r="N14" s="15"/>
     </row>
     <row r="15" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9">
@@ -1867,16 +1854,16 @@
       <c r="C15" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="23" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="4"/>
@@ -1885,7 +1872,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="13"/>
+      <c r="N15" s="15"/>
     </row>
     <row r="16" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
@@ -1908,30 +1895,30 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="13"/>
+      <c r="N16" s="15"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="23">
+      <c r="B17" s="9">
         <v>5</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="25"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="15"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
@@ -1946,36 +1933,36 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="13"/>
+      <c r="N18" s="15"/>
     </row>
     <row r="19" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="23">
+      <c r="B19" s="9">
         <v>6</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D19" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="25"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="15"/>
     </row>
     <row r="20" spans="2:14" ht="120" x14ac:dyDescent="0.25">
       <c r="B20" s="9"/>
@@ -1996,7 +1983,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="13"/>
+      <c r="N20" s="15"/>
     </row>
     <row r="21" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="9">
@@ -2005,10 +1992,10 @@
       <c r="C21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="23" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="4"/>
@@ -2019,7 +2006,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="13"/>
+      <c r="N21" s="15"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="9"/>
@@ -2036,36 +2023,36 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="13"/>
+      <c r="N22" s="15"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="23">
+      <c r="B23" s="9">
         <v>7</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="25"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="15"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="9">
@@ -2086,37 +2073,37 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="13"/>
+      <c r="N24" s="15"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="26">
+      <c r="B25" s="13">
         <v>8</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="25"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="15"/>
     </row>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <v>9</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>40</v>
       </c>
     </row>
